--- a/Result/profitability/2496.xlsx
+++ b/Result/profitability/2496.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>1.275</v>
+        <v>1.1175</v>
       </c>
       <c r="N2" t="n">
-        <v>37.5175</v>
+        <v>37.23</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.00125</v>
+        <v>0.83625</v>
       </c>
       <c r="N3" t="n">
-        <v>21.305</v>
+        <v>21.3175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7137500000000001</v>
+        <v>0.64625</v>
       </c>
       <c r="N4" t="n">
-        <v>6.633749999999999</v>
+        <v>6.651250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5112500000000002</v>
+        <v>0.5012500000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.07625</v>
+        <v>-2.7125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3912500000000001</v>
+        <v>0.2337500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.495</v>
+        <v>-10.715</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1237500000000001</v>
+        <v>0.0075000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-17.67875</v>
+        <v>-17.62875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1037499999999999</v>
+        <v>-0.2062499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-24.21</v>
+        <v>-24.4225</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2496</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>205</v>
+      </c>
+      <c r="D75" t="n">
+        <v>95</v>
+      </c>
+      <c r="E75" t="n">
+        <v>110</v>
+      </c>
+      <c r="F75" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>27</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.91%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.60625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>54.08625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.496969696969697</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.699999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03062511259232559</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.08791208791208793</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.910000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05717092337917484</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
